--- a/docs/DataDictionary042022.xlsx
+++ b/docs/DataDictionary042022.xlsx
@@ -8,18 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ananddivakaran/Documents/Anand/MDS/cpsa/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF669D13-56F1-F443-AAC8-18F38CB9457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AF936FA7-C930-1243-B4CF-D38B48D89124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="18380" windowHeight="15800" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="18380" windowHeight="15800" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2018 and prior" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet4" sheetId="7" r:id="rId2"/>
     <sheet name="Sheet5" sheetId="8" r:id="rId3"/>
     <sheet name="2019 and beyond" sheetId="3" r:id="rId4"/>
-    <sheet name="Statistical Selection" sheetId="4" r:id="rId5"/>
-    <sheet name="Logical Selection" sheetId="5" r:id="rId6"/>
-    <sheet name="Data Treatment" sheetId="6" r:id="rId7"/>
+    <sheet name="Sheet1" sheetId="9" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="10" r:id="rId6"/>
+    <sheet name="Sheet3" sheetId="11" r:id="rId7"/>
+    <sheet name="Statistical Selection" sheetId="4" r:id="rId8"/>
+    <sheet name="Logical Selection" sheetId="5" r:id="rId9"/>
+    <sheet name="Data Treatment" sheetId="6" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Sheet5!$A$1:$D$1</definedName>
@@ -29,6 +32,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'2019 and beyond'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -49,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="740" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="492">
   <si>
     <t>CPSC_Case_Number</t>
   </si>
@@ -894,12 +898,663 @@
   <si>
     <t>Combine 1132,1332, 1383,1306, 1317, 1318, 1356, 5004 to 5021(Toy Vehicles)</t>
   </si>
+  <si>
+    <t>Dataset</t>
+  </si>
+  <si>
+    <t>Record Count</t>
+  </si>
+  <si>
+    <t>Feature Count</t>
+  </si>
+  <si>
+    <t>Train</t>
+  </si>
+  <si>
+    <t>Evaluation</t>
+  </si>
+  <si>
+    <t>Holdout</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>data_year</t>
+  </si>
+  <si>
+    <t>Hospitalized</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>Hospitalized?</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_41',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_42',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_46',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_47',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_48',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_49',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_50',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_51',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_52',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_53',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_54',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_55',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_56',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_57',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_58',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_59',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_60',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_61',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_62',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_63',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_64',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_65',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_66',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_67',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_68',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_69',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_71',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_72',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_73',</t>
+  </si>
+  <si>
+    <t>'cat__Diagnosis_74',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_30',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_31',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_32',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_33',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_34',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_35',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_36',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_37',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_38',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_75',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_76',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_77',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_79',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_80',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_81',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_82',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_83',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_84',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_85',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_87',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_88',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_89',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_92',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_93',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_94',</t>
+  </si>
+  <si>
+    <t>'cat__Location_0',</t>
+  </si>
+  <si>
+    <t>'cat__Location_1',</t>
+  </si>
+  <si>
+    <t>'cat__Location_2',</t>
+  </si>
+  <si>
+    <t>'cat__Location_4',</t>
+  </si>
+  <si>
+    <t>'cat__Location_5',</t>
+  </si>
+  <si>
+    <t>'cat__Location_6',</t>
+  </si>
+  <si>
+    <t>'cat__Location_7',</t>
+  </si>
+  <si>
+    <t>'cat__Location_8',</t>
+  </si>
+  <si>
+    <t>'cat__Location_9',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_0.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_30.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_31.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_32.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_33.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_34.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_35.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_36.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_37.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_38.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_75.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_76.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_77.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_79.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_80.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_81.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_82.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_83.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_84.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_85.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_87.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_88.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_89.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_92.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_93.0',</t>
+  </si>
+  <si>
+    <t>'cat__Body_Part_2_94.0',</t>
+  </si>
+  <si>
+    <t>'cat__Injury_Mechanism_Burn',</t>
+  </si>
+  <si>
+    <t>'cat__Injury_Mechanism_Fall',</t>
+  </si>
+  <si>
+    <t>'cat__Injury_Mechanism_Ingestion/Choking',</t>
+  </si>
+  <si>
+    <t>'cat__Injury_Mechanism_Laceration/Cut',</t>
+  </si>
+  <si>
+    <t>'cat__Injury_Mechanism_Other/Unspecified',</t>
+  </si>
+  <si>
+    <t>'cat__Injury_Mechanism_Struck</t>
+  </si>
+  <si>
+    <t>By',</t>
+  </si>
+  <si>
+    <t>'remainder__Product_1',</t>
+  </si>
+  <si>
+    <t>'remainder__Age_Scaled'</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Injury_Mechanism_Struck</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> remainder__Age_Scaled </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_41  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_42  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_46  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_47  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_48  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_49  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_50  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_51  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_52  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_53  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_54  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_55  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_56  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_57  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_58  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_59  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_60  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_61  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_62  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_63  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_64  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_65  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_66  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_67  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_68  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_69  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_71  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_72  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_73  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Diagnosis_74  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_30  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_31  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_32  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_33  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_34  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_35  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_36  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_37  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_38  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_75  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_76  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_77  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_79  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_80  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_81  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_82  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_83  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_84  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_85  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_87  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_88  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_89  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_92  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_93  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_94  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Location_0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Location_1  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Location_2  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Location_4  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Location_5  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Location_6  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Location_7  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Location_8  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Location_9  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_0.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_30.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_31.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_32.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_33.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_34.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_35.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_36.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_37.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_38.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_75.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_76.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_77.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_79.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_80.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_81.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_82.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_83.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_84.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_85.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_87.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_88.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_89.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_92.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_93.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Body_Part_2_94.0  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Injury_Mechanism_Burn  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Injury_Mechanism_Fall  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Injury_Mechanism_Ingestion/Choking  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Injury_Mechanism_Laceration/Cut  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Injury_Mechanism_Other/Unspecified  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">By  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> remainder__Product_1  </t>
+  </si>
+  <si>
+    <t>Feature List</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> cat__Injury_Mechanism_Struck By</t>
+  </si>
+  <si>
+    <t>read the below classification report and explain how the algorithm is performing?</t>
+  </si>
+  <si>
+    <t>--- Classification Report --- precision recall f1-score support 0 0.98 0.80 0.88 997519 1 0.30 0.82 0.43 99725 accuracy 0.81 1097244 macro avg 0.64 0.81 0.66 1097244 weighted avg 0.92 0.81 0.84 1097244</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -935,6 +1590,17 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FFE3E3E3"/>
+      <name val="Helvetica Neue"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -990,7 +1656,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1001,7 +1667,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1044,12 +1709,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1062,16 +1721,195 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="40">
     <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1090,57 +1928,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1166,14 +1953,26 @@
 </table>
 </file>
 
+<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6E93BCB7-F3D1-794D-B37E-4B9E87C2F0C3}" name="Table4" displayName="Table4" ref="A1:C14" totalsRowShown="0" dataDxfId="3">
+  <autoFilter ref="A1:C14" xr:uid="{6E93BCB7-F3D1-794D-B37E-4B9E87C2F0C3}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{2418A522-5A86-654E-8E23-AA31E4D296E4}" name="Column Name" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{5A8678CF-276B-B849-9710-F3B1266548F7}" name="Null/Missing-Unknown?" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{DD6B0CF7-6CCA-A148-888E-72E6ECE18895}" name="Treatment Description" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{E5CC7609-249C-DA4B-913A-9ABE60D5EFC7}" name="Table5" displayName="Table5" ref="A1:E48" totalsRowShown="0">
   <autoFilter ref="A1:E48" xr:uid="{E5CC7609-249C-DA4B-913A-9ABE60D5EFC7}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{9E833026-55F9-F54F-AF97-FF4395C9C5B3}" name="Product ID" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{91EBB196-61AF-FA41-8719-3805D3D9A775}" name="Reclassified Product ID" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{9E833026-55F9-F54F-AF97-FF4395C9C5B3}" name="Product ID" dataDxfId="39"/>
+    <tableColumn id="2" xr3:uid="{91EBB196-61AF-FA41-8719-3805D3D9A775}" name="Reclassified Product ID" dataDxfId="38"/>
     <tableColumn id="3" xr3:uid="{B9AF7673-D7ED-234F-AE76-02AAE736859A}" name="Injury Year"/>
-    <tableColumn id="4" xr3:uid="{17A42202-BD9E-B446-8E77-5EDC0D79B6D1}" name="Comments" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{17A42202-BD9E-B446-8E77-5EDC0D79B6D1}" name="Comments" dataDxfId="37"/>
     <tableColumn id="5" xr3:uid="{30F78473-1515-BA45-A9E0-F0E8B5B9DD02}" name="Mapped?"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -1181,40 +1980,90 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table22" displayName="Table22" ref="A1:E123" totalsRowShown="0" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table22" displayName="Table22" ref="A1:E123" totalsRowShown="0" dataDxfId="36">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Excel/Tab Variable" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="SAS Variable" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description/Code book" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{A72D9C76-9D00-1A4F-9BE2-BD1E6A51FBC5}" name="Include/Exclude" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{B655C88B-D042-1842-9E2B-05DDDCB2AF91}" name="Include/Exclude Reason" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Excel/Tab Variable" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="SAS Variable" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Description/Code book" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{A72D9C76-9D00-1A4F-9BE2-BD1E6A51FBC5}" name="Include/Exclude" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{B655C88B-D042-1842-9E2B-05DDDCB2AF91}" name="Include/Exclude Reason" dataDxfId="31"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C5CB192C-599A-A349-AEFB-CAE216FF17C1}" name="Table224" displayName="Table224" ref="A1:E26" totalsRowShown="0" headerRowDxfId="8" dataDxfId="7">
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{83FD844F-EDA3-BC4D-9028-139F647067F3}" name="Feature Name" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{8670C7FE-74A6-804A-BA8D-767B87F90511}" name="Cramers_V Score" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{D97EF977-3997-6C46-9944-A86ED9FE15BB}" name="Include for EDA?" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{06107CAF-85C0-104D-8383-565425D80176}" name="Include for Modelling" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{23109576-43E7-E14E-AB01-167038A76F8D}" name="Include/Exclude Reason" dataDxfId="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{2B6ECC91-D0A3-B84A-8A2A-9B90FAB58D36}" name="Table6" displayName="Table6" ref="A3:D7" totalsRowShown="0" headerRowDxfId="30" dataDxfId="29">
+  <autoFilter ref="A3:D7" xr:uid="{2B6ECC91-D0A3-B84A-8A2A-9B90FAB58D36}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{82B86AE3-0438-B74B-A054-B94A6C412D5C}" name="Dataset" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{94904802-BDE5-7641-BC99-33FF19A3A653}" name="Record Count" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{198F9E55-F265-CC43-B89D-ED3ADC8C5349}" name="Percentage" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{6A495048-2138-4546-B42A-A172F6EDC737}" name="Feature Count" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{6E93BCB7-F3D1-794D-B37E-4B9E87C2F0C3}" name="Table4" displayName="Table4" ref="A1:C14" totalsRowShown="0" dataDxfId="6">
-  <autoFilter ref="A1:C14" xr:uid="{6E93BCB7-F3D1-794D-B37E-4B9E87C2F0C3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{3165C2F0-7717-2548-B441-C577232E82EE}" name="Table8" displayName="Table8" ref="A11:D17" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+  <autoFilter ref="A11:D17" xr:uid="{3165C2F0-7717-2548-B441-C577232E82EE}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{F831443B-313B-3249-B7BD-BFF978AB6862}" name="Dataset" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{15D00940-C386-1A4A-B41B-24D59C2C3E7F}" name="Hospitalized" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{F47F9129-2417-FC4A-9E5A-C962D4F0E872}" name="Count" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{B492D953-661D-0242-A38A-D13F0BD2A6F9}" name="Ratio" dataDxfId="19"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{0B65F82F-9BAC-2044-8163-E0AB675714DE}" name="Table9" displayName="Table9" ref="A21:C23" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17">
+  <autoFilter ref="A21:C23" xr:uid="{0B65F82F-9BAC-2044-8163-E0AB675714DE}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{2418A522-5A86-654E-8E23-AA31E4D296E4}" name="Column Name" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{5A8678CF-276B-B849-9710-F3B1266548F7}" name="Null/Missing-Unknown?" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{DD6B0CF7-6CCA-A148-888E-72E6ECE18895}" name="Treatment Description" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{44C9704D-385D-A14D-B728-E78ADEEC9BC7}" name="Hospitalized?" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{EB753D46-2FAB-914D-8391-14A4879A0CD2}" name="Count" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{7EDD0432-07F1-4748-AFF8-8BEB5F8A98F3}" name="Ratio" dataDxfId="14">
+      <calculatedColumnFormula>ROUND(B22/(B22+B21),2)*100</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{6BFF91A3-67B6-8047-9686-2E32310FF69A}" name="Table7" displayName="Table7" ref="A1:C41" totalsRowShown="0">
+  <autoFilter ref="A1:C41" xr:uid="{6BFF91A3-67B6-8047-9686-2E32310FF69A}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{F167DBF1-329C-3445-8739-79638BCB8033}" name="data_year" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{0EC20629-673C-ED49-8FD3-75C2BCB8149B}" name="Hospitalized" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{F2B3A758-16E8-984B-A1B1-EC8366AE0831}" name="Count" dataDxfId="11"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{A07ECBD7-31EA-414E-83F7-589A4C9F06B4}" name="Table10" displayName="Table10" ref="A4:A103" totalsRowShown="0">
+  <autoFilter ref="A4:A103" xr:uid="{A07ECBD7-31EA-414E-83F7-589A4C9F06B4}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{998E4897-0FBD-5D47-852C-8380B29E3B6B}" name="Feature List"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C5CB192C-599A-A349-AEFB-CAE216FF17C1}" name="Table224" displayName="Table224" ref="A1:E26" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <tableColumns count="5">
+    <tableColumn id="1" xr3:uid="{83FD844F-EDA3-BC4D-9028-139F647067F3}" name="Feature Name" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{8670C7FE-74A6-804A-BA8D-767B87F90511}" name="Cramers_V Score" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{D97EF977-3997-6C46-9944-A86ED9FE15BB}" name="Include for EDA?" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{06107CAF-85C0-104D-8383-565425D80176}" name="Include for Modelling" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{23109576-43E7-E14E-AB01-167038A76F8D}" name="Include/Exclude Reason" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -2175,6 +3024,178 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68475FB2-E388-A540-909B-CE0C5CB712D8}">
+  <dimension ref="A1:C14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>211</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="64" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.2">
+      <c r="A3" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="80" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="128" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="96" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="48" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="144" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>229</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A45A5DD6-45C0-7149-8A1C-786742D892F5}">
   <dimension ref="A1:B148"/>
@@ -2244,7 +3265,7 @@
       <c r="A8">
         <v>1527</v>
       </c>
-      <c r="B8" s="24" t="s">
+      <c r="B8" s="21" t="s">
         <v>234</v>
       </c>
     </row>
@@ -2361,289 +3382,289 @@
       </c>
     </row>
     <row r="54" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A54" s="23"/>
+      <c r="A54" s="20"/>
     </row>
     <row r="55" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A55" s="23"/>
+      <c r="A55" s="20"/>
     </row>
     <row r="56" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A56" s="23"/>
+      <c r="A56" s="20"/>
     </row>
     <row r="57" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A57" s="23"/>
+      <c r="A57" s="20"/>
     </row>
     <row r="58" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A58" s="23"/>
+      <c r="A58" s="20"/>
     </row>
     <row r="59" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A59" s="23"/>
+      <c r="A59" s="20"/>
     </row>
     <row r="60" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A60" s="23"/>
+      <c r="A60" s="20"/>
     </row>
     <row r="61" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A61" s="23"/>
+      <c r="A61" s="20"/>
     </row>
     <row r="62" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A62" s="23"/>
+      <c r="A62" s="20"/>
     </row>
     <row r="63" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A63" s="23"/>
+      <c r="A63" s="20"/>
     </row>
     <row r="64" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A64" s="23"/>
+      <c r="A64" s="20"/>
     </row>
     <row r="65" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A65" s="23"/>
+      <c r="A65" s="20"/>
     </row>
     <row r="66" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A66" s="23"/>
+      <c r="A66" s="20"/>
     </row>
     <row r="67" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A67" s="23"/>
+      <c r="A67" s="20"/>
     </row>
     <row r="68" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A68" s="23"/>
+      <c r="A68" s="20"/>
     </row>
     <row r="69" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A69" s="23"/>
+      <c r="A69" s="20"/>
     </row>
     <row r="70" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A70" s="23"/>
+      <c r="A70" s="20"/>
     </row>
     <row r="71" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A71" s="23"/>
+      <c r="A71" s="20"/>
     </row>
     <row r="72" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A72" s="23"/>
+      <c r="A72" s="20"/>
     </row>
     <row r="73" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A73" s="23"/>
+      <c r="A73" s="20"/>
     </row>
     <row r="74" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A74" s="23"/>
+      <c r="A74" s="20"/>
     </row>
     <row r="75" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A75" s="23"/>
+      <c r="A75" s="20"/>
     </row>
     <row r="76" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A76" s="23"/>
+      <c r="A76" s="20"/>
     </row>
     <row r="77" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A77" s="23"/>
+      <c r="A77" s="20"/>
     </row>
     <row r="78" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A78" s="23"/>
+      <c r="A78" s="20"/>
     </row>
     <row r="79" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A79" s="23"/>
+      <c r="A79" s="20"/>
     </row>
     <row r="80" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A80" s="23"/>
+      <c r="A80" s="20"/>
     </row>
     <row r="81" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A81" s="23"/>
+      <c r="A81" s="20"/>
     </row>
     <row r="82" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A82" s="23"/>
+      <c r="A82" s="20"/>
     </row>
     <row r="83" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A83" s="23"/>
+      <c r="A83" s="20"/>
     </row>
     <row r="84" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A84" s="23"/>
+      <c r="A84" s="20"/>
     </row>
     <row r="85" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A85" s="23"/>
+      <c r="A85" s="20"/>
     </row>
     <row r="86" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A86" s="23"/>
+      <c r="A86" s="20"/>
     </row>
     <row r="87" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A87" s="23"/>
+      <c r="A87" s="20"/>
     </row>
     <row r="88" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A88" s="23"/>
+      <c r="A88" s="20"/>
     </row>
     <row r="89" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A89" s="23"/>
+      <c r="A89" s="20"/>
     </row>
     <row r="90" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A90" s="23"/>
+      <c r="A90" s="20"/>
     </row>
     <row r="91" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A91" s="23"/>
+      <c r="A91" s="20"/>
     </row>
     <row r="92" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A92" s="23"/>
+      <c r="A92" s="20"/>
     </row>
     <row r="93" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A93" s="23"/>
+      <c r="A93" s="20"/>
     </row>
     <row r="94" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A94" s="23"/>
+      <c r="A94" s="20"/>
     </row>
     <row r="95" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A95" s="23"/>
+      <c r="A95" s="20"/>
     </row>
     <row r="96" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A96" s="23"/>
+      <c r="A96" s="20"/>
     </row>
     <row r="97" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A97" s="23"/>
+      <c r="A97" s="20"/>
     </row>
     <row r="98" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A98" s="23"/>
+      <c r="A98" s="20"/>
     </row>
     <row r="99" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A99" s="23"/>
+      <c r="A99" s="20"/>
     </row>
     <row r="100" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A100" s="23"/>
+      <c r="A100" s="20"/>
     </row>
     <row r="101" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A101" s="23"/>
+      <c r="A101" s="20"/>
     </row>
     <row r="102" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A102" s="23"/>
+      <c r="A102" s="20"/>
     </row>
     <row r="103" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A103" s="23"/>
+      <c r="A103" s="20"/>
     </row>
     <row r="104" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A104" s="23"/>
+      <c r="A104" s="20"/>
     </row>
     <row r="105" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A105" s="23"/>
+      <c r="A105" s="20"/>
     </row>
     <row r="106" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A106" s="23"/>
+      <c r="A106" s="20"/>
     </row>
     <row r="107" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A107" s="23"/>
+      <c r="A107" s="20"/>
     </row>
     <row r="108" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A108" s="23"/>
+      <c r="A108" s="20"/>
     </row>
     <row r="109" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A109" s="23"/>
+      <c r="A109" s="20"/>
     </row>
     <row r="110" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A110" s="23"/>
+      <c r="A110" s="20"/>
     </row>
     <row r="111" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A111" s="23"/>
+      <c r="A111" s="20"/>
     </row>
     <row r="112" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A112" s="23"/>
+      <c r="A112" s="20"/>
     </row>
     <row r="113" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A113" s="23"/>
+      <c r="A113" s="20"/>
     </row>
     <row r="114" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A114" s="23"/>
+      <c r="A114" s="20"/>
     </row>
     <row r="115" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A115" s="23"/>
+      <c r="A115" s="20"/>
     </row>
     <row r="116" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A116" s="23"/>
+      <c r="A116" s="20"/>
     </row>
     <row r="117" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A117" s="23"/>
+      <c r="A117" s="20"/>
     </row>
     <row r="118" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A118" s="23"/>
+      <c r="A118" s="20"/>
     </row>
     <row r="119" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A119" s="23"/>
+      <c r="A119" s="20"/>
     </row>
     <row r="120" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A120" s="23"/>
+      <c r="A120" s="20"/>
     </row>
     <row r="121" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A121" s="23"/>
+      <c r="A121" s="20"/>
     </row>
     <row r="122" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A122" s="23"/>
+      <c r="A122" s="20"/>
     </row>
     <row r="123" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A123" s="23"/>
+      <c r="A123" s="20"/>
     </row>
     <row r="124" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A124" s="23"/>
+      <c r="A124" s="20"/>
     </row>
     <row r="125" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A125" s="23"/>
+      <c r="A125" s="20"/>
     </row>
     <row r="126" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A126" s="23"/>
+      <c r="A126" s="20"/>
     </row>
     <row r="127" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A127" s="23"/>
+      <c r="A127" s="20"/>
     </row>
     <row r="128" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A128" s="23"/>
+      <c r="A128" s="20"/>
     </row>
     <row r="129" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A129" s="23"/>
+      <c r="A129" s="20"/>
     </row>
     <row r="130" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A130" s="23"/>
+      <c r="A130" s="20"/>
     </row>
     <row r="131" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A131" s="23"/>
+      <c r="A131" s="20"/>
     </row>
     <row r="132" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A132" s="23"/>
+      <c r="A132" s="20"/>
     </row>
     <row r="133" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A133" s="23"/>
+      <c r="A133" s="20"/>
     </row>
     <row r="134" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A134" s="23"/>
+      <c r="A134" s="20"/>
     </row>
     <row r="135" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A135" s="23"/>
+      <c r="A135" s="20"/>
     </row>
     <row r="136" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A136" s="23"/>
+      <c r="A136" s="20"/>
     </row>
     <row r="137" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A137" s="23"/>
+      <c r="A137" s="20"/>
     </row>
     <row r="138" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A138" s="23"/>
+      <c r="A138" s="20"/>
     </row>
     <row r="139" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A139" s="23"/>
+      <c r="A139" s="20"/>
     </row>
     <row r="140" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A140" s="23"/>
+      <c r="A140" s="20"/>
     </row>
     <row r="141" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A141" s="23"/>
+      <c r="A141" s="20"/>
     </row>
     <row r="142" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A142" s="23"/>
+      <c r="A142" s="20"/>
     </row>
     <row r="143" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A143" s="23"/>
+      <c r="A143" s="20"/>
     </row>
     <row r="144" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A144" s="23"/>
+      <c r="A144" s="20"/>
     </row>
     <row r="145" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A145" s="23"/>
+      <c r="A145" s="20"/>
     </row>
     <row r="146" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A146" s="23"/>
+      <c r="A146" s="20"/>
     </row>
     <row r="147" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A147" s="23"/>
+      <c r="A147" s="20"/>
     </row>
     <row r="148" spans="1:1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A148" s="23"/>
+      <c r="A148" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2655,17 +3676,17 @@
   <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="31.5" style="26" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="31.5" style="23" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" t="s">
         <v>249</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="23" t="s">
         <v>261</v>
       </c>
       <c r="C1" t="s">
@@ -2679,10 +3700,10 @@
       </c>
     </row>
     <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A2" s="25">
+      <c r="A2" s="22">
         <v>394</v>
       </c>
-      <c r="B2" s="26">
+      <c r="B2" s="23">
         <v>394</v>
       </c>
       <c r="C2" t="s">
@@ -2696,10 +3717,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
+      <c r="A3">
         <v>556</v>
       </c>
-      <c r="B3" s="26">
+      <c r="B3" s="23">
         <v>556</v>
       </c>
       <c r="C3" t="s">
@@ -2713,10 +3734,10 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
+      <c r="A4">
         <v>569</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="23" t="s">
         <v>263</v>
       </c>
       <c r="C4" t="s">
@@ -2730,10 +3751,10 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
+      <c r="A5">
         <v>574</v>
       </c>
-      <c r="B5" s="26">
+      <c r="B5" s="23">
         <v>5016</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -2744,10 +3765,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
+      <c r="A6">
         <v>876</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="23" t="s">
         <v>265</v>
       </c>
       <c r="C6" t="s">
@@ -2761,10 +3782,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="4">
+      <c r="A7">
         <v>897</v>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="23">
         <v>5016</v>
       </c>
       <c r="E7" t="s">
@@ -2772,10 +3793,10 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="4">
+      <c r="A8">
         <v>899</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="23">
         <v>5016</v>
       </c>
       <c r="E8" t="s">
@@ -2783,10 +3804,10 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A9" s="4">
+      <c r="A9">
         <v>1132</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="23" t="s">
         <v>274</v>
       </c>
       <c r="C9" t="s">
@@ -2800,10 +3821,10 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="4">
+      <c r="A10">
         <v>1145</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="23" t="s">
         <v>266</v>
       </c>
       <c r="C10" t="s">
@@ -2817,10 +3838,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A11" s="4">
+      <c r="A11">
         <v>1317</v>
       </c>
-      <c r="B11" s="26">
+      <c r="B11" s="23">
         <v>5021</v>
       </c>
       <c r="C11" t="s">
@@ -2831,10 +3852,10 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="4">
+      <c r="A12">
         <v>1329</v>
       </c>
-      <c r="B12" s="26">
+      <c r="B12" s="23">
         <v>5023</v>
       </c>
       <c r="E12" t="s">
@@ -2842,10 +3863,10 @@
       </c>
     </row>
     <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A13" s="4">
+      <c r="A13">
         <v>1381</v>
       </c>
-      <c r="B13" s="26">
+      <c r="B13" s="23">
         <v>1381</v>
       </c>
       <c r="C13" t="s">
@@ -2859,10 +3880,10 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A14" s="4">
+      <c r="A14">
         <v>1394</v>
       </c>
-      <c r="B14" s="26">
+      <c r="B14" s="23">
         <v>1394</v>
       </c>
       <c r="C14" t="s">
@@ -2876,10 +3897,10 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A15" s="4">
+      <c r="A15">
         <v>1395</v>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="23">
         <v>1395</v>
       </c>
       <c r="C15" t="s">
@@ -2893,10 +3914,10 @@
       </c>
     </row>
     <row r="16" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A16" s="4">
+      <c r="A16">
         <v>1417</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="23" t="s">
         <v>270</v>
       </c>
       <c r="C16" t="s">
@@ -2910,10 +3931,10 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A17" s="4">
+      <c r="A17">
         <v>1465</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="23" t="s">
         <v>271</v>
       </c>
       <c r="C17" t="s">
@@ -2927,10 +3948,10 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A18" s="4">
+      <c r="A18">
         <v>1466</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="23" t="s">
         <v>271</v>
       </c>
       <c r="C18" t="s">
@@ -2944,10 +3965,10 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="4">
+      <c r="A19">
         <v>1527</v>
       </c>
-      <c r="B19" s="26">
+      <c r="B19" s="23">
         <v>1527</v>
       </c>
       <c r="E19" t="s">
@@ -2955,10 +3976,10 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="4">
+      <c r="A20">
         <v>1543</v>
       </c>
-      <c r="B20" s="26">
+      <c r="B20" s="23">
         <v>1552</v>
       </c>
       <c r="E20" t="s">
@@ -2966,10 +3987,10 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="4">
+      <c r="A21">
         <v>1545</v>
       </c>
-      <c r="B21" s="26">
+      <c r="B21" s="23">
         <v>1552</v>
       </c>
       <c r="E21" t="s">
@@ -2977,10 +3998,10 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="4">
+      <c r="A22">
         <v>1552</v>
       </c>
-      <c r="B22" s="26">
+      <c r="B22" s="23">
         <v>1552</v>
       </c>
       <c r="C22" t="s">
@@ -2994,10 +4015,10 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A23" s="4">
+      <c r="A23">
         <v>1606</v>
       </c>
-      <c r="B23" s="26">
+      <c r="B23" s="23">
         <v>1606</v>
       </c>
       <c r="C23" t="s">
@@ -3011,10 +4032,10 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A24" s="4">
+      <c r="A24">
         <v>1618</v>
       </c>
-      <c r="B24" s="26">
+      <c r="B24" s="23">
         <v>1618</v>
       </c>
       <c r="C24" t="s">
@@ -3028,10 +4049,10 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A25" s="4">
+      <c r="A25">
         <v>1620</v>
       </c>
-      <c r="B25" s="26">
+      <c r="B25" s="23">
         <v>1620</v>
       </c>
       <c r="C25" t="s">
@@ -3045,10 +4066,10 @@
       </c>
     </row>
     <row r="26" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A26" s="4">
+      <c r="A26">
         <v>1629</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="23">
         <v>1629</v>
       </c>
       <c r="C26" t="s">
@@ -3062,10 +4083,10 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" s="4">
+      <c r="A27">
         <v>1706</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="1">
         <v>1706</v>
       </c>
       <c r="C27" t="s">
@@ -3079,10 +4100,10 @@
       </c>
     </row>
     <row r="28" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A28" s="4">
+      <c r="A28">
         <v>1707</v>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="1">
         <v>1707</v>
       </c>
       <c r="C28" t="s">
@@ -3096,10 +4117,10 @@
       </c>
     </row>
     <row r="29" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A29" s="4">
+      <c r="A29">
         <v>1710</v>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="1">
         <v>1710</v>
       </c>
       <c r="C29" t="s">
@@ -3113,10 +4134,10 @@
       </c>
     </row>
     <row r="30" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A30" s="4">
+      <c r="A30">
         <v>1841</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="23">
         <v>1841</v>
       </c>
       <c r="C30" t="s">
@@ -3130,10 +4151,10 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A31" s="4">
+      <c r="A31">
         <v>1855</v>
       </c>
-      <c r="B31" s="26">
+      <c r="B31" s="23">
         <v>1145</v>
       </c>
       <c r="C31" t="s">
@@ -3147,10 +4168,10 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A32" s="4">
+      <c r="A32">
         <v>1909</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="23">
         <v>1909</v>
       </c>
       <c r="C32" t="s">
@@ -3164,10 +4185,10 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A33" s="4">
+      <c r="A33">
         <v>3215</v>
       </c>
-      <c r="B33" s="26">
+      <c r="B33" s="23">
         <v>3215</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -3178,10 +4199,10 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A34" s="4">
+      <c r="A34">
         <v>4802</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="23">
         <v>4802</v>
       </c>
       <c r="C34" t="s">
@@ -3195,10 +4216,10 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="160" x14ac:dyDescent="0.2">
-      <c r="A35" s="4">
+      <c r="A35">
         <v>5004</v>
       </c>
-      <c r="B35" s="26">
+      <c r="B35" s="23">
         <v>1395</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -3209,10 +4230,10 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A36" s="4">
+      <c r="A36">
         <v>5016</v>
       </c>
-      <c r="B36" s="26">
+      <c r="B36" s="23">
         <v>5016</v>
       </c>
       <c r="C36" t="s">
@@ -3226,10 +4247,10 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A37" s="4">
+      <c r="A37">
         <v>5017</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="23" t="s">
         <v>235</v>
       </c>
       <c r="E37" t="s">
@@ -3237,10 +4258,10 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" s="4">
+      <c r="A38">
         <v>5019</v>
       </c>
-      <c r="B38" s="26" t="s">
+      <c r="B38" s="23" t="s">
         <v>235</v>
       </c>
       <c r="E38" t="s">
@@ -3248,10 +4269,10 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" s="4">
+      <c r="A39">
         <v>5020</v>
       </c>
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="23" t="s">
         <v>235</v>
       </c>
       <c r="E39" t="s">
@@ -3259,10 +4280,10 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" s="4">
+      <c r="A40">
         <v>5021</v>
       </c>
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="23" t="s">
         <v>235</v>
       </c>
       <c r="E40" t="s">
@@ -3270,10 +4291,10 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
+      <c r="A41">
         <v>5022</v>
       </c>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="23" t="s">
         <v>236</v>
       </c>
       <c r="E41" t="s">
@@ -3281,10 +4302,10 @@
       </c>
     </row>
     <row r="42" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" s="4">
+      <c r="A42">
         <v>5023</v>
       </c>
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="23" t="s">
         <v>236</v>
       </c>
       <c r="E42" t="s">
@@ -3292,10 +4313,10 @@
       </c>
     </row>
     <row r="43" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="4">
+      <c r="A43">
         <v>5024</v>
       </c>
-      <c r="B43" s="26" t="s">
+      <c r="B43" s="23" t="s">
         <v>236</v>
       </c>
       <c r="E43" t="s">
@@ -3303,10 +4324,10 @@
       </c>
     </row>
     <row r="44" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="4">
+      <c r="A44">
         <v>5025</v>
       </c>
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="23" t="s">
         <v>236</v>
       </c>
       <c r="E44" t="s">
@@ -3314,10 +4335,10 @@
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="4">
+      <c r="A45">
         <v>5042</v>
       </c>
-      <c r="B45" s="26">
+      <c r="B45" s="23">
         <v>5022</v>
       </c>
       <c r="E45" t="s">
@@ -3325,10 +4346,10 @@
       </c>
     </row>
     <row r="46" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="4">
+      <c r="A46">
         <v>5043</v>
       </c>
-      <c r="B46" s="26" t="s">
+      <c r="B46" s="23" t="s">
         <v>235</v>
       </c>
       <c r="E46" t="s">
@@ -3336,10 +4357,10 @@
       </c>
     </row>
     <row r="47" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="4">
+      <c r="A47">
         <v>5045</v>
       </c>
-      <c r="B47" s="26" t="s">
+      <c r="B47" s="23" t="s">
         <v>237</v>
       </c>
       <c r="E47" t="s">
@@ -3347,10 +4368,10 @@
       </c>
     </row>
     <row r="48" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A48" s="4">
+      <c r="A48">
         <v>5046</v>
       </c>
-      <c r="B48" s="26" t="s">
+      <c r="B48" s="23" t="s">
         <v>237</v>
       </c>
       <c r="E48" t="s">
@@ -4703,6 +5724,1849 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B466BEBC-D374-B34F-8FA3-5CF9A5B10B7A}">
+  <dimension ref="A3:D23"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" style="24" customWidth="1"/>
+    <col min="3" max="3" width="11.83203125" customWidth="1"/>
+    <col min="4" max="4" width="14.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="25" t="s">
+        <v>275</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="B4" s="26">
+        <v>5120468</v>
+      </c>
+      <c r="C4" s="18">
+        <v>70</v>
+      </c>
+      <c r="D4" s="18">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="B5" s="26">
+        <v>1097244</v>
+      </c>
+      <c r="C5" s="18">
+        <v>15</v>
+      </c>
+      <c r="D5" s="18">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="B6" s="26">
+        <v>1097244</v>
+      </c>
+      <c r="C6" s="18">
+        <v>15</v>
+      </c>
+      <c r="D6" s="18">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B7" s="26">
+        <f>SUM(B4:B6)</f>
+        <v>7314956</v>
+      </c>
+      <c r="C7" s="18">
+        <v>100</v>
+      </c>
+      <c r="D7" s="18">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="B11" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="C11" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="D11" s="29" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="B12" s="29">
+        <v>0</v>
+      </c>
+      <c r="C12" s="29">
+        <v>4655082</v>
+      </c>
+      <c r="D12" s="29">
+        <f>ROUND((C12/(C12+C13))*100,2)</f>
+        <v>90.91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="29" t="s">
+        <v>278</v>
+      </c>
+      <c r="B13" s="29">
+        <v>1</v>
+      </c>
+      <c r="C13" s="29">
+        <v>465386</v>
+      </c>
+      <c r="D13" s="29">
+        <f>ROUND((C13/(C13+C12))*100,2)</f>
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="B14" s="30">
+        <v>0</v>
+      </c>
+      <c r="C14" s="29">
+        <v>997519</v>
+      </c>
+      <c r="D14" s="29">
+        <f>ROUND((C14/(C14+C15))*100,2)</f>
+        <v>90.91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="B15" s="30">
+        <v>1</v>
+      </c>
+      <c r="C15" s="29">
+        <v>99725</v>
+      </c>
+      <c r="D15" s="29">
+        <f>ROUND((C15/(C15+C14))*100,2)</f>
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="29" t="s">
+        <v>280</v>
+      </c>
+      <c r="B16" s="30">
+        <v>0</v>
+      </c>
+      <c r="C16" s="29">
+        <v>997518</v>
+      </c>
+      <c r="D16" s="29">
+        <f>ROUND((C16/(C16+C17))*100,2)</f>
+        <v>90.91</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="29" t="s">
+        <v>280</v>
+      </c>
+      <c r="B17" s="30">
+        <v>1</v>
+      </c>
+      <c r="C17" s="29">
+        <v>99726</v>
+      </c>
+      <c r="D17" s="29">
+        <f>ROUND((C17/(C17+C16))*100,2)</f>
+        <v>9.09</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>283</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="18">
+        <v>0</v>
+      </c>
+      <c r="B22" s="26">
+        <v>6650119</v>
+      </c>
+      <c r="C22" s="18">
+        <f>ROUND(B22/(B22+B23),2)*100</f>
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="18">
+        <v>1</v>
+      </c>
+      <c r="B23" s="26">
+        <v>664837</v>
+      </c>
+      <c r="C23" s="18">
+        <f>ROUND(B23/(B23+B22),2)*100</f>
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="3">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBABEE57-1775-6043-8CB4-AB04C14B89D2}">
+  <dimension ref="A1:DA41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="136.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A1" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>283</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="G1" t="s">
+        <v>289</v>
+      </c>
+      <c r="H1" t="s">
+        <v>290</v>
+      </c>
+      <c r="I1" t="s">
+        <v>291</v>
+      </c>
+      <c r="J1" t="s">
+        <v>292</v>
+      </c>
+      <c r="K1" t="s">
+        <v>293</v>
+      </c>
+      <c r="L1" t="s">
+        <v>294</v>
+      </c>
+      <c r="M1" t="s">
+        <v>295</v>
+      </c>
+      <c r="N1" t="s">
+        <v>296</v>
+      </c>
+      <c r="O1" t="s">
+        <v>297</v>
+      </c>
+      <c r="P1" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>299</v>
+      </c>
+      <c r="R1" t="s">
+        <v>300</v>
+      </c>
+      <c r="S1" t="s">
+        <v>301</v>
+      </c>
+      <c r="T1" t="s">
+        <v>302</v>
+      </c>
+      <c r="U1" t="s">
+        <v>303</v>
+      </c>
+      <c r="V1" t="s">
+        <v>304</v>
+      </c>
+      <c r="W1" t="s">
+        <v>305</v>
+      </c>
+      <c r="X1" t="s">
+        <v>306</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>307</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>308</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>309</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>310</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>311</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>312</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>313</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>314</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>315</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>316</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>317</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>318</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>319</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>320</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>321</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>322</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>323</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>324</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>325</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>326</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>327</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>328</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>329</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>330</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>331</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>332</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>333</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>334</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>335</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>336</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>337</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>338</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>339</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>340</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>341</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>342</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>343</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>344</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>345</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>346</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>347</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>348</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>349</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>350</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>351</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>352</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>353</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>354</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>355</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>356</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>357</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>358</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>359</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>360</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>361</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>362</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>363</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>364</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>365</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>366</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>367</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>368</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>369</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>370</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>371</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>372</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>373</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>374</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>375</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>376</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>377</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>378</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>379</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>380</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>381</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>382</v>
+      </c>
+      <c r="CW1" t="s">
+        <v>383</v>
+      </c>
+      <c r="CX1" t="s">
+        <v>384</v>
+      </c>
+      <c r="CY1" t="s">
+        <v>385</v>
+      </c>
+      <c r="CZ1" t="s">
+        <v>386</v>
+      </c>
+      <c r="DA1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="2" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="27">
+        <v>2005</v>
+      </c>
+      <c r="B2" s="28">
+        <v>0</v>
+      </c>
+      <c r="C2" s="28">
+        <v>236967</v>
+      </c>
+    </row>
+    <row r="3" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="27">
+        <v>2005</v>
+      </c>
+      <c r="B3" s="28">
+        <v>1</v>
+      </c>
+      <c r="C3" s="28">
+        <v>15254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="27">
+        <v>2006</v>
+      </c>
+      <c r="B4" s="28">
+        <v>0</v>
+      </c>
+      <c r="C4" s="28">
+        <v>238747</v>
+      </c>
+    </row>
+    <row r="5" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="27">
+        <v>2006</v>
+      </c>
+      <c r="B5" s="28">
+        <v>1</v>
+      </c>
+      <c r="C5" s="28">
+        <v>15748</v>
+      </c>
+    </row>
+    <row r="6" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="27">
+        <v>2007</v>
+      </c>
+      <c r="B6" s="28">
+        <v>0</v>
+      </c>
+      <c r="C6" s="28">
+        <v>242403</v>
+      </c>
+    </row>
+    <row r="7" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="27">
+        <v>2007</v>
+      </c>
+      <c r="B7" s="28">
+        <v>1</v>
+      </c>
+      <c r="C7" s="28">
+        <v>16439</v>
+      </c>
+    </row>
+    <row r="8" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="27">
+        <v>2008</v>
+      </c>
+      <c r="B8" s="28">
+        <v>0</v>
+      </c>
+      <c r="C8" s="28">
+        <v>244657</v>
+      </c>
+    </row>
+    <row r="9" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="27">
+        <v>2008</v>
+      </c>
+      <c r="B9" s="28">
+        <v>1</v>
+      </c>
+      <c r="C9" s="28">
+        <v>17293</v>
+      </c>
+    </row>
+    <row r="10" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="27">
+        <v>2009</v>
+      </c>
+      <c r="B10" s="28">
+        <v>0</v>
+      </c>
+      <c r="C10" s="28">
+        <v>254571</v>
+      </c>
+    </row>
+    <row r="11" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="27">
+        <v>2009</v>
+      </c>
+      <c r="B11" s="28">
+        <v>1</v>
+      </c>
+      <c r="C11" s="28">
+        <v>19747</v>
+      </c>
+    </row>
+    <row r="12" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="27">
+        <v>2010</v>
+      </c>
+      <c r="B12" s="28">
+        <v>0</v>
+      </c>
+      <c r="C12" s="28">
+        <v>263406</v>
+      </c>
+    </row>
+    <row r="13" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="27">
+        <v>2010</v>
+      </c>
+      <c r="B13" s="28">
+        <v>1</v>
+      </c>
+      <c r="C13" s="28">
+        <v>20564</v>
+      </c>
+    </row>
+    <row r="14" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="27">
+        <v>2011</v>
+      </c>
+      <c r="B14" s="28">
+        <v>0</v>
+      </c>
+      <c r="C14" s="28">
+        <v>257017</v>
+      </c>
+    </row>
+    <row r="15" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="27">
+        <v>2011</v>
+      </c>
+      <c r="B15" s="28">
+        <v>1</v>
+      </c>
+      <c r="C15" s="28">
+        <v>20500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:105" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="27">
+        <v>2012</v>
+      </c>
+      <c r="B16" s="28">
+        <v>0</v>
+      </c>
+      <c r="C16" s="28">
+        <v>254802</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="27">
+        <v>2012</v>
+      </c>
+      <c r="B17" s="28">
+        <v>1</v>
+      </c>
+      <c r="C17" s="28">
+        <v>21240</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="27">
+        <v>2013</v>
+      </c>
+      <c r="B18" s="28">
+        <v>0</v>
+      </c>
+      <c r="C18" s="28">
+        <v>241922</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="27">
+        <v>2013</v>
+      </c>
+      <c r="B19" s="28">
+        <v>1</v>
+      </c>
+      <c r="C19" s="28">
+        <v>21896</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="27">
+        <v>2014</v>
+      </c>
+      <c r="B20" s="28">
+        <v>0</v>
+      </c>
+      <c r="C20" s="28">
+        <v>236169</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="27">
+        <v>2014</v>
+      </c>
+      <c r="B21" s="28">
+        <v>1</v>
+      </c>
+      <c r="C21" s="28">
+        <v>21056</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="27">
+        <v>2015</v>
+      </c>
+      <c r="B22" s="28">
+        <v>0</v>
+      </c>
+      <c r="C22" s="28">
+        <v>229419</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="27">
+        <v>2015</v>
+      </c>
+      <c r="B23" s="28">
+        <v>1</v>
+      </c>
+      <c r="C23" s="28">
+        <v>21950</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="27">
+        <v>2016</v>
+      </c>
+      <c r="B24" s="28">
+        <v>0</v>
+      </c>
+      <c r="C24" s="28">
+        <v>238688</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="27">
+        <v>2016</v>
+      </c>
+      <c r="B25" s="28">
+        <v>1</v>
+      </c>
+      <c r="C25" s="28">
+        <v>23927</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="27">
+        <v>2017</v>
+      </c>
+      <c r="B26" s="28">
+        <v>0</v>
+      </c>
+      <c r="C26" s="28">
+        <v>244791</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="27">
+        <v>2017</v>
+      </c>
+      <c r="B27" s="28">
+        <v>1</v>
+      </c>
+      <c r="C27" s="28">
+        <v>26011</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="27">
+        <v>2018</v>
+      </c>
+      <c r="B28" s="28">
+        <v>0</v>
+      </c>
+      <c r="C28" s="28">
+        <v>225755</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="27">
+        <v>2018</v>
+      </c>
+      <c r="B29" s="28">
+        <v>1</v>
+      </c>
+      <c r="C29" s="28">
+        <v>27390</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="27">
+        <v>2019</v>
+      </c>
+      <c r="B30" s="28">
+        <v>0</v>
+      </c>
+      <c r="C30" s="28">
+        <v>223061</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="27">
+        <v>2019</v>
+      </c>
+      <c r="B31" s="28">
+        <v>1</v>
+      </c>
+      <c r="C31" s="28">
+        <v>28016</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="27">
+        <v>2020</v>
+      </c>
+      <c r="B32" s="28">
+        <v>0</v>
+      </c>
+      <c r="C32" s="28">
+        <v>187255</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="27">
+        <v>2020</v>
+      </c>
+      <c r="B33" s="28">
+        <v>1</v>
+      </c>
+      <c r="C33" s="28">
+        <v>29286</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="27">
+        <v>2021</v>
+      </c>
+      <c r="B34" s="28">
+        <v>0</v>
+      </c>
+      <c r="C34" s="28">
+        <v>208390</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="27">
+        <v>2021</v>
+      </c>
+      <c r="B35" s="28">
+        <v>1</v>
+      </c>
+      <c r="C35" s="28">
+        <v>29897</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="27">
+        <v>2022</v>
+      </c>
+      <c r="B36" s="28">
+        <v>0</v>
+      </c>
+      <c r="C36" s="28">
+        <v>198672</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="27">
+        <v>2022</v>
+      </c>
+      <c r="B37" s="28">
+        <v>1</v>
+      </c>
+      <c r="C37" s="28">
+        <v>27652</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="27">
+        <v>2023</v>
+      </c>
+      <c r="B38" s="28">
+        <v>0</v>
+      </c>
+      <c r="C38" s="28">
+        <v>207123</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="27">
+        <v>2023</v>
+      </c>
+      <c r="B39" s="28">
+        <v>1</v>
+      </c>
+      <c r="C39" s="28">
+        <v>29635</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="27">
+        <v>2024</v>
+      </c>
+      <c r="B40" s="28">
+        <v>0</v>
+      </c>
+      <c r="C40" s="28">
+        <v>221267</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="27">
+        <v>2024</v>
+      </c>
+      <c r="B41" s="28">
+        <v>1</v>
+      </c>
+      <c r="C41" s="28">
+        <v>31885</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6510E547-8375-0A40-9F74-47ECA5CBFCA4}">
+  <dimension ref="A1:CV114"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="35.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="30" width="16.5" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="16" bestFit="1" customWidth="1"/>
+    <col min="32" max="56" width="17.1640625" bestFit="1" customWidth="1"/>
+    <col min="57" max="65" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="67" max="91" width="20.5" bestFit="1" customWidth="1"/>
+    <col min="92" max="92" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="93" max="93" width="24.1640625" bestFit="1" customWidth="1"/>
+    <col min="94" max="94" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="95" max="95" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="96" max="96" width="35.6640625" bestFit="1" customWidth="1"/>
+    <col min="97" max="97" width="25.5" bestFit="1" customWidth="1"/>
+    <col min="98" max="98" width="3.83203125" bestFit="1" customWidth="1"/>
+    <col min="99" max="99" width="20" bestFit="1" customWidth="1"/>
+    <col min="100" max="100" width="19.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C1" t="s">
+        <v>392</v>
+      </c>
+      <c r="D1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E1" t="s">
+        <v>394</v>
+      </c>
+      <c r="F1" t="s">
+        <v>395</v>
+      </c>
+      <c r="G1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I1" t="s">
+        <v>398</v>
+      </c>
+      <c r="J1" t="s">
+        <v>399</v>
+      </c>
+      <c r="K1" t="s">
+        <v>400</v>
+      </c>
+      <c r="L1" t="s">
+        <v>401</v>
+      </c>
+      <c r="M1" t="s">
+        <v>402</v>
+      </c>
+      <c r="N1" t="s">
+        <v>403</v>
+      </c>
+      <c r="O1" t="s">
+        <v>404</v>
+      </c>
+      <c r="P1" t="s">
+        <v>405</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>406</v>
+      </c>
+      <c r="R1" t="s">
+        <v>407</v>
+      </c>
+      <c r="S1" t="s">
+        <v>408</v>
+      </c>
+      <c r="T1" t="s">
+        <v>409</v>
+      </c>
+      <c r="U1" t="s">
+        <v>410</v>
+      </c>
+      <c r="V1" t="s">
+        <v>411</v>
+      </c>
+      <c r="W1" t="s">
+        <v>412</v>
+      </c>
+      <c r="X1" t="s">
+        <v>413</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>414</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>415</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>416</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>417</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>418</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>419</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>420</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>421</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>422</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>423</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>424</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>425</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>426</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>427</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>428</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>429</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>430</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>431</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>432</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>433</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>434</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>435</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>436</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>437</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>438</v>
+      </c>
+      <c r="AX1" t="s">
+        <v>439</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>440</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>441</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>442</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>443</v>
+      </c>
+      <c r="BC1" t="s">
+        <v>444</v>
+      </c>
+      <c r="BD1" t="s">
+        <v>445</v>
+      </c>
+      <c r="BE1" t="s">
+        <v>446</v>
+      </c>
+      <c r="BF1" t="s">
+        <v>447</v>
+      </c>
+      <c r="BG1" t="s">
+        <v>448</v>
+      </c>
+      <c r="BH1" t="s">
+        <v>449</v>
+      </c>
+      <c r="BI1" t="s">
+        <v>450</v>
+      </c>
+      <c r="BJ1" t="s">
+        <v>451</v>
+      </c>
+      <c r="BK1" t="s">
+        <v>452</v>
+      </c>
+      <c r="BL1" t="s">
+        <v>453</v>
+      </c>
+      <c r="BM1" t="s">
+        <v>454</v>
+      </c>
+      <c r="BN1" t="s">
+        <v>455</v>
+      </c>
+      <c r="BO1" t="s">
+        <v>456</v>
+      </c>
+      <c r="BP1" t="s">
+        <v>457</v>
+      </c>
+      <c r="BQ1" t="s">
+        <v>458</v>
+      </c>
+      <c r="BR1" t="s">
+        <v>459</v>
+      </c>
+      <c r="BS1" t="s">
+        <v>460</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>461</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>462</v>
+      </c>
+      <c r="BV1" t="s">
+        <v>463</v>
+      </c>
+      <c r="BW1" t="s">
+        <v>464</v>
+      </c>
+      <c r="BX1" t="s">
+        <v>465</v>
+      </c>
+      <c r="BY1" t="s">
+        <v>466</v>
+      </c>
+      <c r="BZ1" t="s">
+        <v>467</v>
+      </c>
+      <c r="CA1" t="s">
+        <v>468</v>
+      </c>
+      <c r="CB1" t="s">
+        <v>469</v>
+      </c>
+      <c r="CC1" t="s">
+        <v>470</v>
+      </c>
+      <c r="CD1" t="s">
+        <v>471</v>
+      </c>
+      <c r="CE1" t="s">
+        <v>472</v>
+      </c>
+      <c r="CF1" t="s">
+        <v>473</v>
+      </c>
+      <c r="CG1" t="s">
+        <v>474</v>
+      </c>
+      <c r="CH1" t="s">
+        <v>475</v>
+      </c>
+      <c r="CI1" t="s">
+        <v>476</v>
+      </c>
+      <c r="CJ1" t="s">
+        <v>477</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>478</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>479</v>
+      </c>
+      <c r="CM1" t="s">
+        <v>480</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>481</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>482</v>
+      </c>
+      <c r="CP1" t="s">
+        <v>483</v>
+      </c>
+      <c r="CQ1" t="s">
+        <v>484</v>
+      </c>
+      <c r="CR1" t="s">
+        <v>485</v>
+      </c>
+      <c r="CS1" t="s">
+        <v>388</v>
+      </c>
+      <c r="CT1" t="s">
+        <v>486</v>
+      </c>
+      <c r="CU1" t="s">
+        <v>487</v>
+      </c>
+      <c r="CV1" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="5" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="6" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="8" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="10" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="11" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="12" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="13" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="14" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="15" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:100" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" ht="20" x14ac:dyDescent="0.2">
+      <c r="A110" s="31" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A114" s="20" t="s">
+        <v>491</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BB4E4A1-C4CA-074C-BA5A-5F7D873D1C24}">
   <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
@@ -4711,7 +7575,7 @@
     <col min="2" max="2" width="7.6640625" style="1" customWidth="1"/>
     <col min="3" max="3" width="8.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="9.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="22.1640625" style="8" customWidth="1"/>
+    <col min="5" max="5" width="22.1640625" style="7" customWidth="1"/>
     <col min="6" max="6" width="14.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.83203125" customWidth="1"/>
   </cols>
@@ -4729,410 +7593,410 @@
       <c r="D1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="96" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>0.02</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="6" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>0.02</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>0.06</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>0.03</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="6" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>0.26</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>0.11</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="E10" s="6" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>0.28000000000000003</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>201</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="6" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5" t="s">
+      <c r="B12" s="4"/>
+      <c r="C12" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5" t="s">
+      <c r="B13" s="4"/>
+      <c r="C13" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="6" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5" t="s">
+      <c r="B14" s="4"/>
+      <c r="C14" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="6" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="112" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5" t="s">
+      <c r="B15" s="4"/>
+      <c r="C15" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>0.11</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>0.05</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E17" s="7" t="s">
+      <c r="E17" s="6" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5" t="s">
+      <c r="B18" s="4"/>
+      <c r="C18" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5" t="s">
+      <c r="B19" s="4"/>
+      <c r="C19" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>0.23</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="6" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>0.08</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="6" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5" t="s">
+      <c r="B22" s="4"/>
+      <c r="C22" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E22" s="7" t="s">
+      <c r="E22" s="6" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5" t="s">
+      <c r="B23" s="4"/>
+      <c r="C23" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="E23" s="6" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="6" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>0.15</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="E25" s="6" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5" t="s">
+      <c r="B26" s="4"/>
+      <c r="C26" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="6" t="s">
         <v>191</v>
       </c>
     </row>
@@ -5144,473 +8008,300 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4078738-A86C-D84F-9E84-635E8EB5013A}">
   <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.1640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="4" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="4"/>
+    <col min="1" max="1" width="22.1640625" customWidth="1"/>
+    <col min="2" max="2" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="33" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="112" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="C2" s="12" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="112" x14ac:dyDescent="0.2">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="15" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="48" x14ac:dyDescent="0.2">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="B4" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="12" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="15" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="80" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="12" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="96" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="15" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="112" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C9" s="16" t="s">
+      <c r="C9" s="15" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="12" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="112" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="15" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="112" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
+      <c r="A12" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" s="12" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="15" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A14" s="13" t="s">
+      <c r="A14" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="B14" s="9"/>
-      <c r="C14" s="13" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="12" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="256" x14ac:dyDescent="0.2">
-      <c r="A15" s="13" t="s">
+      <c r="A15" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="96" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="144" x14ac:dyDescent="0.2">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="15" t="s">
+      <c r="B17" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="15" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="144" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="12" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="144" x14ac:dyDescent="0.2">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="B19" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="15" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="96" x14ac:dyDescent="0.2">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="96" x14ac:dyDescent="0.2">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="15" t="s">
+      <c r="B21" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="15" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="48" x14ac:dyDescent="0.2">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="12" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="80" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
+      <c r="A23" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="B23" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="15" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="144" x14ac:dyDescent="0.2">
-      <c r="A24" s="13" t="s">
+      <c r="A24" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" s="12" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="144" x14ac:dyDescent="0.2">
-      <c r="A25" s="13" t="s">
+      <c r="A25" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="B25" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="15" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="113" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="13" t="s">
+      <c r="A26" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="17" t="s">
+      <c r="B26" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="C26" s="18" t="s">
+      <c r="C26" s="17" t="s">
         <v>210</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68475FB2-E388-A540-909B-CE0C5CB712D8}">
-  <dimension ref="A1:C14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="14.1640625" customWidth="1"/>
-    <col min="2" max="2" width="24.83203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="34.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="C1" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="64" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="80" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="80" x14ac:dyDescent="0.2">
-      <c r="A5" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="96" x14ac:dyDescent="0.2">
-      <c r="A6" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B6" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="128" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="96" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="48" x14ac:dyDescent="0.2">
-      <c r="A10" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="48" x14ac:dyDescent="0.2">
-      <c r="A11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="48" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="48" x14ac:dyDescent="0.2">
-      <c r="A13" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="144" x14ac:dyDescent="0.2">
-      <c r="A14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="22" t="s">
-        <v>225</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>229</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
-</worksheet>
 </file>